--- a/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,91</t>
+          <t>3,07; 9,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,02</t>
+          <t>1,6; 7,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 11,93</t>
+          <t>3,42; 11,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,1</t>
+          <t>1,0; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,63</t>
+          <t>0,54; 4,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 12,95</t>
+          <t>4,05; 13,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,67</t>
+          <t>2,58; 6,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,27</t>
+          <t>1,39; 4,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,33</t>
+          <t>4,3; 10,36</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,66</t>
+          <t>1,13; 4,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,11</t>
+          <t>1,84; 6,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,95</t>
+          <t>4,98; 11,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,91</t>
+          <t>1,79; 6,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,64</t>
+          <t>1,68; 5,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,73</t>
+          <t>3,61; 9,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,39</t>
+          <t>1,84; 4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,05</t>
+          <t>2,21; 4,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,64</t>
+          <t>4,83; 9,26</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,45</t>
+          <t>1,41; 6,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,42</t>
+          <t>1,84; 6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 12,55</t>
+          <t>5,03; 12,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,8</t>
+          <t>1,27; 6,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,17</t>
+          <t>1,16; 5,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 12,53</t>
+          <t>5,61; 12,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,06</t>
+          <t>1,61; 5,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,92</t>
+          <t>1,9; 4,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,15</t>
+          <t>6,23; 11,16</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,41</t>
+          <t>1,59; 6,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,39</t>
+          <t>1,3; 6,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,88</t>
+          <t>4,92; 11,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,35; 3,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,69</t>
+          <t>3,48; 9,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,24</t>
+          <t>4,49; 9,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,15</t>
+          <t>1,31; 4,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,7</t>
+          <t>2,79; 6,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,36</t>
+          <t>5,25; 9,16</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,79</t>
+          <t>2,54; 4,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,7</t>
+          <t>2,48; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,87</t>
+          <t>6,24; 9,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,98</t>
+          <t>2,0; 3,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,84</t>
+          <t>2,62; 4,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,64</t>
+          <t>5,56; 8,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,02</t>
+          <t>2,46; 3,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,33</t>
+          <t>2,79; 4,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,48</t>
+          <t>6,17; 8,6</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5322</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4522</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12471</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4436; 13406</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2112; 9583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1966; 6883</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1447; 8814</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>668; 5106</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2490; 8041</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7485; 18723</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3544; 12287</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5110; 12326</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5748</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12719</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9284</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10682</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15031</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15702</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>23401</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2675; 11494</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3840; 12703</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7941; 18320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4796; 16412</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4303; 14073</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6565; 16805</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9260; 23127</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10280; 22476</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16478; 31584</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6460</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14085</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4805</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17916</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9905</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>32001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2196; 10181</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3451; 12040</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8741; 21294</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2015; 9762</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2155; 10278</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11869; 26099</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5078; 15749</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7096; 18624</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23998; 43017</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5799</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21501</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10541</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19643</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8366</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>41144</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2726; 11538</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2241; 10384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13513; 30471</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>632; 6396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6034; 17223</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13709; 28988</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4602; 14104</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9638; 23380</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>30462; 53130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24802</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24276</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52763</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>50484</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>104888</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>17982; 34398</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17392; 33867</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41484; 64809</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15008; 30035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19382; 35710</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>42303; 65963</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>35902; 57350</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>40111; 64109</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87935; 122650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,28</t>
+          <t>2,9; 9,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,28</t>
+          <t>1,87; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,97</t>
+          <t>3,03; 12,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,06</t>
+          <t>1,07; 6,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,11</t>
+          <t>0,54; 4,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 13,09</t>
+          <t>3,8; 12,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,46</t>
+          <t>2,63; 6,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,8</t>
+          <t>1,54; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,36</t>
+          <t>4,58; 11,08</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,87</t>
+          <t>1,11; 4,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,09</t>
+          <t>1,9; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 11,5</t>
+          <t>5,27; 11,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,12</t>
+          <t>1,96; 5,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,5</t>
+          <t>1,72; 5,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,24</t>
+          <t>3,4; 8,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,58</t>
+          <t>1,9; 4,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,84</t>
+          <t>2,15; 5,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,26</t>
+          <t>4,94; 9,52</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,52</t>
+          <t>1,4; 6,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,42</t>
+          <t>1,52; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,25</t>
+          <t>5,21; 12,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,16</t>
+          <t>1,32; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,51</t>
+          <t>1,14; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,34</t>
+          <t>5,25; 12,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,0</t>
+          <t>1,81; 4,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,98</t>
+          <t>1,91; 4,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,16</t>
+          <t>6,09; 11,02</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,73</t>
+          <t>1,56; 6,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,01</t>
+          <t>1,29; 6,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,1</t>
+          <t>5,14; 10,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,55</t>
+          <t>0,35; 3,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,93</t>
+          <t>3,45; 10,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,49</t>
+          <t>4,25; 9,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,02</t>
+          <t>1,33; 4,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,76</t>
+          <t>2,86; 6,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,16</t>
+          <t>5,17; 9,04</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,86</t>
+          <t>2,46; 4,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,84</t>
+          <t>2,57; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,74</t>
+          <t>6,17; 9,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,99</t>
+          <t>1,9; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,83</t>
+          <t>2,5; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,68</t>
+          <t>5,4; 8,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,93</t>
+          <t>2,37; 3,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,45</t>
+          <t>2,78; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,6</t>
+          <t>6,31; 8,62</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4436; 13406</t>
+          <t>4185; 13885</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2112; 9583</t>
+          <t>2464; 9994</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1966; 6883</t>
+          <t>1745; 7188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1447; 8814</t>
+          <t>1562; 9361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>668; 5106</t>
+          <t>666; 5720</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2490; 8041</t>
+          <t>2335; 7799</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7485; 18723</t>
+          <t>7629; 18805</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3544; 12287</t>
+          <t>3931; 12191</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5110; 12326</t>
+          <t>5443; 13185</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2675; 11494</t>
+          <t>2616; 10737</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3840; 12703</t>
+          <t>3953; 12714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7941; 18320</t>
+          <t>8392; 18739</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4796; 16412</t>
+          <t>5259; 15897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4303; 14073</t>
+          <t>4402; 14398</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6565; 16805</t>
+          <t>6186; 16149</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9260; 23127</t>
+          <t>9595; 23568</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10280; 22476</t>
+          <t>9980; 23236</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16478; 31584</t>
+          <t>16839; 32493</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2196; 10181</t>
+          <t>2181; 9513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3451; 12040</t>
+          <t>2840; 11394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8741; 21294</t>
+          <t>9055; 22012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2015; 9762</t>
+          <t>2097; 9477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2155; 10278</t>
+          <t>2126; 10008</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11869; 26099</t>
+          <t>11103; 26316</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5078; 15749</t>
+          <t>5694; 15682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7096; 18624</t>
+          <t>7158; 18198</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23998; 43017</t>
+          <t>23469; 42485</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2726; 11538</t>
+          <t>2672; 10937</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2241; 10384</t>
+          <t>2231; 10517</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13513; 30471</t>
+          <t>14110; 29617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>632; 6396</t>
+          <t>638; 6421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6034; 17223</t>
+          <t>5978; 17402</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13709; 28988</t>
+          <t>12981; 28886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4602; 14104</t>
+          <t>4655; 14364</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9638; 23380</t>
+          <t>9893; 24023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30462; 53130</t>
+          <t>29969; 52412</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17982; 34398</t>
+          <t>17440; 32935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17392; 33867</t>
+          <t>18023; 34452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41484; 64809</t>
+          <t>41031; 64200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15008; 30035</t>
+          <t>14277; 29047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19382; 35710</t>
+          <t>18514; 35369</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42303; 65963</t>
+          <t>41076; 65804</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35902; 57350</t>
+          <t>34629; 58113</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40111; 64109</t>
+          <t>40100; 63666</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87935; 122650</t>
+          <t>89985; 122939</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,61</t>
+          <t>1,02; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,59</t>
+          <t>0,54; 4,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,5</t>
+          <t>3,39; 11,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,44</t>
+          <t>3,16; 9,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,61</t>
+          <t>1,97; 8,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,69</t>
+          <t>2,97; 11,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,49</t>
+          <t>2,59; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,77</t>
+          <t>1,55; 5,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,08</t>
+          <t>3,98; 9,46</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,54</t>
+          <t>1,87; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,1</t>
+          <t>1,8; 5,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,76</t>
+          <t>3,19; 8,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,92</t>
+          <t>1,08; 4,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,62</t>
+          <t>1,84; 6,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,88</t>
+          <t>5,43; 12,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,67</t>
+          <t>1,72; 4,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,0</t>
+          <t>2,24; 5,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,52</t>
+          <t>4,81; 9,81</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,09</t>
+          <t>1,31; 5,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,08</t>
+          <t>1,13; 5,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,66</t>
+          <t>5,5; 12,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,98</t>
+          <t>1,47; 6,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,37</t>
+          <t>1,78; 6,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,44</t>
+          <t>5,38; 12,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,98</t>
+          <t>1,77; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,87</t>
+          <t>1,86; 4,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,02</t>
+          <t>6,02; 11,11</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,38%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,38</t>
+          <t>0,36; 3,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,09</t>
+          <t>3,44; 9,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,79</t>
+          <t>4,34; 9,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,57</t>
+          <t>1,49; 6,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,04</t>
+          <t>1,29; 6,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,46</t>
+          <t>6,12; 12,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,09</t>
+          <t>1,32; 4,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,94</t>
+          <t>2,85; 6,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,04</t>
+          <t>5,93; 9,92</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,65</t>
+          <t>1,89; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,92</t>
+          <t>2,58; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,65</t>
+          <t>5,36; 8,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,86</t>
+          <t>2,57; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,78</t>
+          <t>2,46; 4,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,65</t>
+          <t>6,82; 10,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,98</t>
+          <t>2,46; 4,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,42</t>
+          <t>2,7; 4,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,62</t>
+          <t>6,42; 8,68</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>8155</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>5322</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>6552</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4185; 13885</t>
+          <t>1490; 8871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2464; 9994</t>
+          <t>667; 5754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1745; 7188</t>
+          <t>1714; 5761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1562; 9361</t>
+          <t>4565; 14321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>666; 5720</t>
+          <t>2599; 10560</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2335; 7799</t>
+          <t>1545; 6107</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7629; 18805</t>
+          <t>7507; 19333</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3931; 12191</t>
+          <t>3966; 13479</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5443; 13185</t>
+          <t>4086; 9712</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9284</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8516</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5748</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7274</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12719</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8428</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>20720</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2616; 10737</t>
+          <t>5018; 15860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3953; 12714</t>
+          <t>4598; 14446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8392; 18739</t>
+          <t>5002; 13966</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5259; 15897</t>
+          <t>2542; 11000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4402; 14398</t>
+          <t>3837; 12744</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6186; 16149</t>
+          <t>7897; 18474</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9595; 23568</t>
+          <t>8667; 22133</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9980; 23236</t>
+          <t>10392; 23470</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16839; 32493</t>
+          <t>14537; 29653</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4805</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16823</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>5100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>6460</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14085</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4805</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>31226</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2181; 9513</t>
+          <t>2082; 9190</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2840; 11394</t>
+          <t>2111; 9639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9055; 22012</t>
+          <t>10962; 24764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2097; 9477</t>
+          <t>2290; 10078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2126; 10008</t>
+          <t>3345; 12042</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11103; 26316</t>
+          <t>9448; 22533</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5694; 15682</t>
+          <t>5577; 15944</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7158; 18198</t>
+          <t>6939; 18393</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23469; 42485</t>
+          <t>22557; 41624</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10541</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18968</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5799</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5220</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21501</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10541</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>41977</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2672; 10937</t>
+          <t>647; 6401</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2231; 10517</t>
+          <t>5957; 16807</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14110; 29617</t>
+          <t>12705; 27465</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>638; 6421</t>
+          <t>2558; 10980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5978; 17402</t>
+          <t>2235; 11036</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12981; 28886</t>
+          <t>15644; 31207</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4655; 14364</t>
+          <t>4625; 14579</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9893; 24023</t>
+          <t>9876; 23186</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29969; 52412</t>
+          <t>32526; 54351</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17440; 32935</t>
+          <t>14210; 29957</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18023; 34452</t>
+          <t>19093; 35833</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41031; 64200</t>
+          <t>37489; 59236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14277; 29047</t>
+          <t>18213; 33912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18514; 35369</t>
+          <t>17194; 32882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41076; 65804</t>
+          <t>42864; 66630</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34629; 58113</t>
+          <t>35876; 58667</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40100; 63666</t>
+          <t>38814; 62323</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89985; 122939</t>
+          <t>85194; 115246</t>
         </is>
       </c>
     </row>
